--- a/src/src/main/resources/template/APM_Supplier.xlsx
+++ b/src/src/main/resources/template/APM_Supplier.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\503310146\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{894A7609-D51C-4BA4-9282-3A06186E0FC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14AA452B-831E-4A37-B120-CE489E54A1F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="datalist" sheetId="1" r:id="rId1"/>
@@ -607,6 +607,18 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="landscape" horizontalDpi="300" verticalDpi="300"/>
   <headerFooter alignWithMargins="0"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{723254F0-8E93-4595-AF11-7635D4283208}">
+          <x14:formula1>
+            <xm:f>类型!$A$2:$A$8</xm:f>
+          </x14:formula1>
+          <xm:sqref>H2:H1048576</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+  </extLst>
 </worksheet>
 </file>
 

--- a/src/src/main/resources/template/APM_Supplier.xlsx
+++ b/src/src/main/resources/template/APM_Supplier.xlsx
@@ -8,13 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\503310146\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14AA452B-831E-4A37-B120-CE489E54A1F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C43573CF-1C14-48ED-8FC0-723ACB518A6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="datalist" sheetId="1" r:id="rId1"/>
     <sheet name="类型" sheetId="2" r:id="rId2"/>
+    <sheet name="必填字段填写说明" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -32,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="17">
   <si>
     <t>名称</t>
   </si>
@@ -75,6 +76,7 @@
       <rPr>
         <sz val="10"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>制造商</t>
@@ -96,6 +98,7 @@
       <rPr>
         <sz val="10"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>维修商</t>
@@ -112,6 +115,7 @@
       <rPr>
         <sz val="10"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>制造商</t>
@@ -133,6 +137,7 @@
       <rPr>
         <sz val="10"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>维修商</t>
@@ -155,6 +160,7 @@
       <rPr>
         <sz val="10"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>制造商</t>
@@ -176,13 +182,16 @@
   <si>
     <t>uid</t>
     <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>必填项字段，未填写不支持导入</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -196,22 +205,31 @@
     <font>
       <sz val="9"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="微软雅黑"/>
       <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
   </fonts>
@@ -235,7 +253,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -247,6 +265,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -674,4 +695,33 @@
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{651D6472-10CB-4CB4-9593-B2E097F4AFE9}">
+  <dimension ref="A1:A3"/>
+  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="39" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="6" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A2" s="6" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A3" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="6" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/src/src/main/resources/template/APM_Supplier.xlsx
+++ b/src/src/main/resources/template/APM_Supplier.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\503310146\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C43573CF-1C14-48ED-8FC0-723ACB518A6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C38D210-3434-4DBC-8CA6-A31848A9A22A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -253,21 +253,22 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -586,30 +587,30 @@
   <dimension ref="A1:H1"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="31.7109375" customWidth="1"/>
-    <col min="2" max="2" width="19" customWidth="1"/>
-    <col min="3" max="3" width="20.85546875" customWidth="1"/>
-    <col min="4" max="4" width="18.5703125" customWidth="1"/>
-    <col min="5" max="5" width="10.28515625" customWidth="1"/>
-    <col min="6" max="6" width="14.140625" customWidth="1"/>
-    <col min="7" max="7" width="13.28515625" customWidth="1"/>
-    <col min="8" max="8" width="24.28515625" customWidth="1"/>
+    <col min="1" max="1" width="31.7109375" style="5" customWidth="1"/>
+    <col min="2" max="2" width="19" style="5" customWidth="1"/>
+    <col min="3" max="3" width="20.85546875" style="5" customWidth="1"/>
+    <col min="4" max="4" width="18.5703125" style="5" customWidth="1"/>
+    <col min="5" max="5" width="10.28515625" style="5" customWidth="1"/>
+    <col min="6" max="6" width="14.140625" style="5" customWidth="1"/>
+    <col min="7" max="7" width="13.28515625" style="5" customWidth="1"/>
+    <col min="8" max="8" width="24.28515625" style="5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="6" t="s">
         <v>1</v>
       </c>
       <c r="D1" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="6" t="s">
         <v>2</v>
       </c>
       <c r="F1" s="4" t="s">
@@ -618,7 +619,7 @@
       <c r="G1" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="6" t="s">
         <v>3</v>
       </c>
     </row>
@@ -652,42 +653,42 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="2" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="2" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A4" s="3" t="s">
+      <c r="A4" s="2" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A5" s="3" t="s">
+      <c r="A5" s="2" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="2" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A7" s="3" t="s">
+      <c r="A7" s="2" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A8" s="3" t="s">
+      <c r="A8" s="2" t="s">
         <v>9</v>
       </c>
     </row>
@@ -706,17 +707,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:1" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="3" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A2" s="6" t="s">
+      <c r="A2" s="3" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A3" s="6" t="s">
+      <c r="A3" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/src/src/main/resources/template/APM_Supplier.xlsx
+++ b/src/src/main/resources/template/APM_Supplier.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26130"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26924"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\503310146\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C38D210-3434-4DBC-8CA6-A31848A9A22A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98B55509-7655-4DEE-9292-5D78E3CAD6AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -267,7 +267,7 @@
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -587,40 +587,40 @@
   <dimension ref="A1:H1"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="31.7109375" style="5" customWidth="1"/>
-    <col min="2" max="2" width="19" style="5" customWidth="1"/>
-    <col min="3" max="3" width="20.85546875" style="5" customWidth="1"/>
-    <col min="4" max="4" width="18.5703125" style="5" customWidth="1"/>
-    <col min="5" max="5" width="10.28515625" style="5" customWidth="1"/>
-    <col min="6" max="6" width="14.140625" style="5" customWidth="1"/>
-    <col min="7" max="7" width="13.28515625" style="5" customWidth="1"/>
-    <col min="8" max="8" width="24.28515625" style="5" customWidth="1"/>
+    <col min="1" max="1" width="19" style="5" customWidth="1"/>
+    <col min="2" max="2" width="20.85546875" style="5" customWidth="1"/>
+    <col min="3" max="3" width="18.5703125" style="5" customWidth="1"/>
+    <col min="4" max="4" width="10.28515625" style="5" customWidth="1"/>
+    <col min="5" max="5" width="14.140625" style="5" customWidth="1"/>
+    <col min="6" max="6" width="13.28515625" style="5" customWidth="1"/>
+    <col min="7" max="7" width="24.28515625" style="5" customWidth="1"/>
+    <col min="8" max="8" width="31.7109375" style="5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="G1" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="H1" s="7" t="s">
         <v>15</v>
-      </c>
-      <c r="B1" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="E1" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="G1" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="H1" s="6" t="s">
-        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -636,7 +636,7 @@
           <x14:formula1>
             <xm:f>类型!$A$2:$A$8</xm:f>
           </x14:formula1>
-          <xm:sqref>H2:H1048576</xm:sqref>
+          <xm:sqref>G2:H1048576</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>

--- a/src/src/main/resources/template/APM_Supplier.xlsx
+++ b/src/src/main/resources/template/APM_Supplier.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\503310146\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98B55509-7655-4DEE-9292-5D78E3CAD6AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F8A174A-BB21-4BCD-B17B-1302321FCD3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="datalist" sheetId="1" r:id="rId1"/>
@@ -636,7 +636,7 @@
           <x14:formula1>
             <xm:f>类型!$A$2:$A$8</xm:f>
           </x14:formula1>
-          <xm:sqref>G2:H1048576</xm:sqref>
+          <xm:sqref>G2:G1048576</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
